--- a/app/templates/copias/Template_GranAgregado-copia.xlsx
+++ b/app/templates/copias/Template_GranAgregado-copia.xlsx
@@ -31788,7 +31788,11 @@
       <c r="E11" s="820"/>
       <c r="F11" s="819"/>
       <c r="G11" s="820"/>
-      <c r="H11" s="756"/>
+      <c r="H11" s="756" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="I11" s="744"/>
       <c r="L11" s="285" t="s">
         <v>468</v>
@@ -38776,8 +38780,10 @@
       <c r="B9" s="439" t="s">
         <v>348</v>
       </c>
-      <c r="C9" s="899" t="s">
-        <v>360</v>
+      <c r="C9" s="899" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D9" s="900"/>
       <c r="F9" s="590" t="s">
@@ -38796,12 +38802,16 @@
       <c r="B10" s="439" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="899" t="s">
-        <v>360</v>
+      <c r="C10" s="899" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D10" s="900"/>
-      <c r="F10" s="726" t="s">
-        <v>360</v>
+      <c r="F10" s="726" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G10" s="470">
         <f>+FORMATO!H11</f>

--- a/app/templates/copias/Template_GranAgregado-copia.xlsx
+++ b/app/templates/copias/Template_GranAgregado-copia.xlsx
@@ -38813,10 +38813,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G10" s="470">
-        <f>+FORMATO!H11</f>
-        <v>0</v>
-      </c>
+      <c r="G10" s="470"/>
       <c r="H10" s="470"/>
       <c r="I10" s="470"/>
       <c r="J10" s="470"/>
@@ -38911,7 +38908,7 @@
         <v>300</v>
       </c>
       <c r="H14" s="538">
-        <f>+FORMATO!D35</f>
+        <f>+IF(C10="Global",FORMATO!D21,FORMATO!D35)</f>
         <v>0</v>
       </c>
       <c r="I14" s="442">
@@ -38945,7 +38942,7 @@
         <v>301</v>
       </c>
       <c r="H15" s="539">
-        <f>+FORMATO!D37</f>
+        <f>+IF(C10="Global",FORMATO!D22,FORMATO!D36)</f>
         <v>0</v>
       </c>
       <c r="I15" s="444">
